--- a/docs/Files/Mid-format_model/ODYM_T6_SortingToRefurbishmentRate_V1.0.xlsx
+++ b/docs/Files/Mid-format_model/ODYM_T6_SortingToRefurbishmentRate_V1.0.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7044A19B-0BC3-410D-8279-106091D568DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7110B8-15EB-4963-B0E6-2545AD66D510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -1185,7 +1185,7 @@
         <v>93</v>
       </c>
       <c r="D2">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1211,7 +1211,7 @@
         <v>96</v>
       </c>
       <c r="D3">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="E3">
         <v>1</v>
